--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487997_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487997_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9279</v>
+        <v>5.1514</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5909</v>
+        <v>3.8849</v>
       </c>
       <c r="F2" t="n">
-        <v>3.337</v>
+        <v>1.2665</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4501</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3642</v>
+        <v>-0.4981</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0859</v>
+        <v>1.4542</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4943</v>
+        <v>1.668</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1596</v>
+        <v>1.1703</v>
       </c>
       <c r="L2" t="n">
-        <v>3.3347</v>
+        <v>0.4977</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0442</v>
+        <v>-0.7119</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7953</v>
+        <v>-1.6684</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2488</v>
+        <v>0.9565</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.5769</v>
+        <v>2.3787</v>
       </c>
       <c r="Q2" t="n">
-        <v>-5.1538</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5769</v>
+        <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4512</v>
+        <v>-0.2606</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6469</v>
+        <v>0.1396</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8043</v>
+        <v>-0.4002</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6036</v>
+        <v>2.0772</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6036</v>
+        <v>2.0772</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2718</v>
+        <v>4.1396</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2299</v>
+        <v>1.7573</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0419</v>
+        <v>2.3823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9560999999999999</v>
+        <v>4.4501</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4981</v>
+        <v>1.3642</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4542</v>
+        <v>3.0859</v>
       </c>
       <c r="J3" t="n">
-        <v>1.668</v>
+        <v>5.4943</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1703</v>
+        <v>2.1596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4977</v>
+        <v>3.3347</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7119</v>
+        <v>-1.0442</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6684</v>
+        <v>-0.7953</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9565</v>
+        <v>-0.2488</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3787</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-5.1538</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3787</v>
+        <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1402</v>
+        <v>1.6628</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4847</v>
+        <v>0.8132</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6249</v>
+        <v>0.8496</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0772</v>
+        <v>0.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0772</v>
+        <v>0.6036</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9706</v>
+        <v>3.5694</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0026</v>
+        <v>2.433</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9679</v>
+        <v>1.1364</v>
       </c>
       <c r="G4" t="n">
         <v>1.1673</v>
@@ -766,13 +766,13 @@
         <v>3.568</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1284</v>
+        <v>-0.5295</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5064</v>
+        <v>-0.076</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.622</v>
+        <v>-0.4535</v>
       </c>
       <c r="V4" t="n">
         <v>1.5441</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9782</v>
+        <v>2.026</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2203</v>
+        <v>2.5488</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.242</v>
+        <v>-0.5228</v>
       </c>
       <c r="G5" t="n">
         <v>0.2698</v>
@@ -844,13 +844,13 @@
         <v>2.5769</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4809</v>
+        <v>-0.4332</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3192</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1617</v>
+        <v>-0.4425</v>
       </c>
       <c r="V5" t="n">
         <v>0.6036</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.269</v>
+        <v>0.9635</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1975</v>
+        <v>0.6674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.2961</v>
       </c>
       <c r="G6" t="n">
         <v>0.228</v>
@@ -922,13 +922,13 @@
         <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0799</v>
+        <v>-0.3854</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6864</v>
+        <v>-0.2165</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3936</v>
+        <v>-0.1689</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2666</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>Z. POPE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5221</v>
+        <v>0.3657</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4915</v>
+        <v>-1.2085</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0306</v>
+        <v>1.5742</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1168</v>
+        <v>-1.465</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5108</v>
+        <v>-2.2436</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6274999999999999</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8664</v>
+        <v>-0.1588</v>
       </c>
       <c r="K7" t="n">
-        <v>2.381</v>
+        <v>-1.4522</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5145</v>
+        <v>1.2935</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9832</v>
+        <v>-1.3062</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8702</v>
+        <v>-0.7914</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.113</v>
+        <v>-0.5148</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
         <v>2.9733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5947</v>
+        <v>-0.5589</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.444</v>
+        <v>-0.0586</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1506</v>
+        <v>-0.5003</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6036</v>
+        <v>0.4074</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8701</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. POPE</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.652</v>
+        <v>-0.3578</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0858</v>
+        <v>-0.3272</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4338</v>
+        <v>-0.0306</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.465</v>
+        <v>-0.1168</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.2436</v>
+        <v>0.5108</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7786999999999999</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1588</v>
+        <v>1.8664</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4522</v>
+        <v>2.381</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2935</v>
+        <v>-0.5145</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3062</v>
+        <v>-1.9832</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7914</v>
+        <v>-1.8702</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5148</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R8" t="n">
         <v>2.9733</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5767</v>
+        <v>-0.4304</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.2798</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6407</v>
+        <v>-0.1506</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4074</v>
+        <v>-0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4074</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2297</v>
+        <v>-0.4967</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9049</v>
+        <v>-2.5369</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6752</v>
+        <v>2.0403</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9085</v>
@@ -1156,13 +1156,13 @@
         <v>2.7751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5788</v>
+        <v>0.1542</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3192</v>
+        <v>0.0488</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2596</v>
+        <v>0.1054</v>
       </c>
       <c r="V9" t="n">
         <v>-0.337</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2943</v>
+        <v>-1.0177</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3092</v>
+        <v>-2.1449</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0149</v>
+        <v>1.1272</v>
       </c>
       <c r="G10" t="n">
         <v>0.0589</v>
@@ -1234,13 +1234,13 @@
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1747</v>
+        <v>0.1019</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2496</v>
+        <v>-0.0853</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.1872</v>
       </c>
       <c r="V10" t="n">
         <v>0.4074</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.7194</v>
+        <v>14.3434</v>
       </c>
       <c r="E11" t="n">
-        <v>4.449800000000002</v>
+        <v>5.073899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>9.269600000000001</v>
+        <v>9.269599999999999</v>
       </c>
       <c r="G11" t="n">
         <v>4.639900000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6791999999999997</v>
+        <v>-0.6791999999999995</v>
       </c>
       <c r="I11" t="n">
         <v>5.3191</v>
@@ -1303,7 +1303,7 @@
         <v>0.8219000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>5.946800000000001</v>
+        <v>5.946799999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-15.858</v>
@@ -1312,13 +1312,13 @@
         <v>21.8045</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3031</v>
+        <v>-0.6790999999999997</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3292000000000001</v>
+        <v>0.2947000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9739000000000002</v>
+        <v>-0.9738</v>
       </c>
       <c r="V11" t="n">
         <v>4.4361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8694</v>
+        <v>2.6772</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5193</v>
+        <v>2.1305</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3501</v>
+        <v>0.5467</v>
       </c>
       <c r="G12" t="n">
         <v>2.3976</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9335</v>
+        <v>-0.1257</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6643</v>
+        <v>-0.0531</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2692</v>
+        <v>-0.0727</v>
       </c>
       <c r="V12" t="n">
         <v>0.6036</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5093</v>
+        <v>1.7973</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5099</v>
+        <v>-0.3062</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0192</v>
+        <v>2.1035</v>
       </c>
       <c r="G13" t="n">
         <v>0.1389</v>
@@ -1468,13 +1468,13 @@
         <v>2.1805</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4027</v>
+        <v>-0.1147</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4257</v>
+        <v>-0.222</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0231</v>
+        <v>0.1073</v>
       </c>
       <c r="V13" t="n">
         <v>-0.4074</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3529</v>
+        <v>-1.0499</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.1719</v>
+        <v>-1.3172</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1809</v>
+        <v>0.2673</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3323</v>
+        <v>0.2174</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0089</v>
+        <v>0.6231</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3412</v>
+        <v>-0.4057</v>
       </c>
       <c r="J14" t="n">
-        <v>0.256</v>
+        <v>0.9218</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9351</v>
+        <v>2.1596</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6791</v>
+        <v>-1.2377</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.7044</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0738</v>
+        <v>-1.5365</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.662</v>
+        <v>0.8321</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5947</v>
+        <v>-1.784</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1593</v>
+        <v>0.5167</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4368</v>
+        <v>0.7343</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2774</v>
+        <v>-0.2176</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.4189</v>
+        <v>-1.3633</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0625</v>
+        <v>-1.0701</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3564</v>
+        <v>-0.2932</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1431</v>
+        <v>-0.3323</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.81</v>
+        <v>1.0089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3331</v>
+        <v>-1.3412</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.571</v>
+        <v>0.256</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6111</v>
+        <v>0.9351</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0402</v>
+        <v>-0.6791</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5722</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1989</v>
+        <v>0.0738</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3733</v>
+        <v>-0.662</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1805</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1118</v>
+        <v>-0.1698</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4729</v>
+        <v>-0.3349</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6389</v>
+        <v>0.1651</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7326</v>
+        <v>-1.4463</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1482</v>
+        <v>-0.9044</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8808</v>
+        <v>-0.542</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3965</v>
+        <v>-1.8327</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3135</v>
+        <v>-0.0286</v>
       </c>
       <c r="I16" t="n">
-        <v>0.71</v>
+        <v>-1.8041</v>
       </c>
       <c r="J16" t="n">
-        <v>2.636</v>
+        <v>0.6942</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6886</v>
+        <v>0.7668</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9474</v>
+        <v>-0.0726</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2395</v>
+        <v>-2.5269</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0021</v>
+        <v>-0.7953</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2374</v>
+        <v>-1.7315</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7751</v>
+        <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4834</v>
+        <v>-0.6048</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0476</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5309</v>
+        <v>0.0027</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.9474</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7905</v>
+        <v>-1.6901</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1081</v>
+        <v>0.5557</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6824</v>
+        <v>-2.2458</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8327</v>
+        <v>0.3965</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0286</v>
+        <v>-0.3135</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8041</v>
+        <v>0.71</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6942</v>
+        <v>2.636</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7668</v>
+        <v>1.6886</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0726</v>
+        <v>0.9474</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5269</v>
+        <v>-2.2395</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7953</v>
+        <v>-2.0021</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7315</v>
+        <v>-0.2374</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9822</v>
+        <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9489</v>
+        <v>0.5258</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8112</v>
+        <v>0.3599</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1377</v>
+        <v>0.1659</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.9474</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8224</v>
+        <v>-1.6932</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7247</v>
+        <v>-1.2694</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0977</v>
+        <v>-0.4237</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2174</v>
+        <v>-0.5028</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6231</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4057</v>
+        <v>-1.0446</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9218</v>
+        <v>0.7528</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1596</v>
+        <v>1.2712</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2377</v>
+        <v>-0.5184</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7044</v>
+        <v>-1.2556</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5365</v>
+        <v>-0.7294</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8321</v>
+        <v>-0.5262</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.784</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2558</v>
+        <v>-0.5451</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3268</v>
+        <v>-0.256</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5826</v>
+        <v>-0.2891</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9405</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1953</v>
+        <v>-2.9622</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.575</v>
+        <v>-1.5982</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6203</v>
+        <v>-1.364</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5028</v>
+        <v>-0.745</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5417999999999999</v>
+        <v>-1.625</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0446</v>
+        <v>0.88</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7528</v>
+        <v>1.0988</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2712</v>
+        <v>-0.8336</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5184</v>
+        <v>1.9324</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2556</v>
+        <v>-1.8438</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7294</v>
+        <v>-0.7914</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5262</v>
+        <v>-1.0524</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5858</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0473</v>
+        <v>0.2606</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5616</v>
+        <v>0.1506</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4857</v>
+        <v>0.11</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9405</v>
+        <v>-1.6849</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2071</v>
+        <v>0.1258</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2178</v>
+        <v>-3.9743</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1907</v>
+        <v>-2.0849</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0271</v>
+        <v>-1.8894</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.745</v>
+        <v>-2.2344</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.625</v>
+        <v>-1.161</v>
       </c>
       <c r="I20" t="n">
-        <v>0.88</v>
+        <v>-1.0734</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0988</v>
+        <v>-0.1752</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8336</v>
+        <v>-0.2958</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9324</v>
+        <v>0.1205</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8438</v>
+        <v>-2.0591</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7914</v>
+        <v>-0.8652</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0524</v>
+        <v>-1.1939</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7929</v>
+        <v>-1.784</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1805</v>
+        <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>1.005</v>
+        <v>0.044</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5581</v>
+        <v>0.0726</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4469</v>
+        <v>-0.0285</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.6849</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1258</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5679</v>
+        <v>-4.0146</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5942</v>
+        <v>-3.4055</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9737</v>
+        <v>-0.6091</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2344</v>
+        <v>-2.1431</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.161</v>
+        <v>-1.81</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0734</v>
+        <v>-0.3331</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1752</v>
+        <v>-0.571</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2958</v>
+        <v>-0.6111</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1205</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0591</v>
+        <v>-1.5722</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8652</v>
+        <v>-1.1989</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1939</v>
+        <v>-0.3733</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.784</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5495</v>
+        <v>1.5161</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4368</v>
+        <v>1.1299</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1128</v>
+        <v>0.3862</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="22">
@@ -2125,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.7196</v>
+        <v>-13.7194</v>
       </c>
       <c r="E22" t="n">
-        <v>-9.269500000000001</v>
+        <v>-9.2697</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.45</v>
+        <v>-4.4497</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6399</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6791999999999994</v>
+        <v>0.6791999999999998</v>
       </c>
       <c r="I22" t="n">
         <v>-5.319100000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>9.498799999999999</v>
+        <v>9.498800000000001</v>
       </c>
       <c r="K22" t="n">
         <v>10.3207</v>
@@ -2158,7 +2158,7 @@
         <v>-9.641399999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.4972</v>
+        <v>-4.497200000000001</v>
       </c>
       <c r="P22" t="n">
         <v>-5.9467</v>
@@ -2170,13 +2170,13 @@
         <v>15.8578</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3032</v>
+        <v>1.3031</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9738000000000002</v>
+        <v>0.9738999999999998</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3292</v>
+        <v>0.3293</v>
       </c>
       <c r="V22" t="n">
         <v>-4.4361</v>
@@ -2185,7 +2185,7 @@
         <v>2.0622</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.498399999999999</v>
+        <v>-6.4984</v>
       </c>
     </row>
   </sheetData>
